--- a/InputData/web-app/OCCF/Output Currency Conversion Factors.xlsx
+++ b/InputData/web-app/OCCF/Output Currency Conversion Factors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\web-app\OCCF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-southkorea\InputData\web-app\OCCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B6FEF58-08A4-48D5-A6A7-14155C535D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA38807-15E2-4E49-8980-288C6A38AA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="OCCF-DpMOCU" sheetId="4" r:id="rId3"/>
     <sheet name="OCCF-DpSOCU" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
   <si>
     <t>Source:</t>
   </si>
@@ -87,6 +87,9 @@
     <t>See cpi.xlsx</t>
   </si>
   <si>
+    <t>2012 dollars are worth more than 2018 dollars, so we need a</t>
+  </si>
+  <si>
     <t>value less than 1 in this variable.</t>
   </si>
   <si>
@@ -105,29 +108,35 @@
     <t>Recall, this variable is "dollars per large/medium/small currency output unit"</t>
   </si>
   <si>
-    <t>2012 dollars are worth more than 2020 dollars, so we need a</t>
-  </si>
-  <si>
-    <t>2023 dollars per 2012 dollar</t>
-  </si>
-  <si>
-    <t>billion 2023 dollars</t>
-  </si>
-  <si>
-    <t>million 2023 dollars</t>
-  </si>
-  <si>
-    <t>2023 dollars</t>
-  </si>
-  <si>
-    <t>which in this case is "2012 dollars per 2023 dollar."</t>
+    <t>2019 dollars per 2012 dollar</t>
+  </si>
+  <si>
+    <t>which in this case is "2012 dollars per 2019 dollar."</t>
+  </si>
+  <si>
+    <t>million 2019 dollars</t>
+  </si>
+  <si>
+    <t>billion 2019 dollars</t>
+  </si>
+  <si>
+    <t>USD to KRW</t>
+  </si>
+  <si>
+    <t>2019 average</t>
+  </si>
+  <si>
+    <t>https://www.investing.com/currencies/usd-krw-historical-data</t>
+  </si>
+  <si>
+    <t>2019 dollars</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,6 +148,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -167,21 +184,26 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -198,9 +220,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -238,9 +260,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -273,9 +295,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -308,9 +347,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -484,28 +540,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.26953125" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -513,120 +570,139 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="5"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B17" s="6"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="5"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="6"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="5"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B23" s="6"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>0.75350342301658668</v>
+        <v>0.89805481563188172</v>
       </c>
       <c r="B26" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B30" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B31" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B32" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B33" t="s">
-        <v>19</v>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36">
+        <v>1164.79</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C36" r:id="rId1" xr:uid="{1D3CC4E1-E398-4D6F-B67D-99A925F86565}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -636,23 +712,23 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="31.26953125" customWidth="1"/>
+    <col min="2" max="2" width="31.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2">
-        <f>10^9*About!$A$26</f>
-        <v>753503423.01658666</v>
+      <c r="B2" s="3">
+        <f>10^9*About!$A$26/About!$B$36</f>
+        <v>771001.48149613384</v>
       </c>
     </row>
   </sheetData>
@@ -666,23 +742,23 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="31.26953125" customWidth="1"/>
+    <col min="2" max="2" width="31.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="6">
-        <f>10^6*About!$A$26</f>
-        <v>753503.42301658669</v>
+      <c r="B2" s="3">
+        <f>10^6*About!$A$26/About!$B$36</f>
+        <v>771.00148149613381</v>
       </c>
     </row>
   </sheetData>
@@ -696,26 +772,197 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="31.26953125" customWidth="1"/>
+    <col min="2" max="2" width="31.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2">
-        <f>1*About!A26</f>
-        <v>0.75350342301658668</v>
+      <c r="B2" s="7">
+        <f>About!A26/About!$B$36</f>
+        <v>7.7100148149613387E-4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EE0DCE0-21BD-4BBD-B5BF-DB017A2506C3}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6EF2122-C1FB-4A3B-84B8-29D6F42C74CA}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{704CAEF7-E5E9-4A87-B274-39F747162F2D}"/>
 </file>
--- a/InputData/web-app/OCCF/Output Currency Conversion Factors.xlsx
+++ b/InputData/web-app/OCCF/Output Currency Conversion Factors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-southkorea\InputData\web-app\OCCF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-southkorea\InputData\web-app\OCCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA38807-15E2-4E49-8980-288C6A38AA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8360B5E7-EDDC-4730-8C2D-9AF82BA8A78E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="OCCF-DpMOCU" sheetId="4" r:id="rId3"/>
     <sheet name="OCCF-DpSOCU" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>Source:</t>
   </si>
@@ -130,6 +130,9 @@
   </si>
   <si>
     <t>2019 dollars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">units are in 1000 KWR </t>
   </si>
 </sst>
 </file>
@@ -188,17 +191,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
@@ -220,9 +221,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -260,9 +261,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -295,26 +296,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -347,26 +331,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -540,29 +507,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C38"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" customWidth="1"/>
+    <col min="1" max="1" width="19.453125" customWidth="1"/>
+    <col min="2" max="2" width="26.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -570,80 +537,80 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="6"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="6"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="5"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="6"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="5"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>0.89805481563188172</v>
       </c>
@@ -651,50 +618,55 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B36">
         <v>1164.79</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="7" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -712,23 +684,23 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="31.28515625" customWidth="1"/>
+    <col min="2" max="2" width="31.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B1" s="4" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3">
-        <f>10^9*About!$A$26/About!$B$36</f>
-        <v>771001.48149613384</v>
+      <c r="B2" s="2">
+        <f>(10^9*About!$A$26/About!$B$36)*1000</f>
+        <v>771001481.4961338</v>
       </c>
     </row>
   </sheetData>
@@ -742,23 +714,23 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="31.28515625" customWidth="1"/>
+    <col min="2" max="2" width="31.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B1" s="4" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B1" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3">
-        <f>10^6*About!$A$26/About!$B$36</f>
-        <v>771.00148149613381</v>
+      <c r="B2" s="2">
+        <f>(10^6*About!$A$26/About!$B$36)*1000</f>
+        <v>771001.48149613384</v>
       </c>
     </row>
   </sheetData>
@@ -772,23 +744,23 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="31.28515625" customWidth="1"/>
+    <col min="2" max="2" width="31.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B1" s="4" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B1" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="7">
-        <f>About!A26/About!$B$36</f>
-        <v>7.7100148149613387E-4</v>
+      <c r="B2">
+        <f>(About!A26/About!$B$36)*1000</f>
+        <v>0.7710014814961339</v>
       </c>
     </row>
   </sheetData>
@@ -956,13 +928,36 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EE0DCE0-21BD-4BBD-B5BF-DB017A2506C3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EE0DCE0-21BD-4BBD-B5BF-DB017A2506C3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6EF2122-C1FB-4A3B-84B8-29D6F42C74CA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6EF2122-C1FB-4A3B-84B8-29D6F42C74CA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{704CAEF7-E5E9-4A87-B274-39F747162F2D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{704CAEF7-E5E9-4A87-B274-39F747162F2D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>